--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Springs Window Fashions</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7393630dd79bd972</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d238e5b67ffdea1b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Google Cloud Platform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b5033226455ae</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9c5bfb77638de8</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GK POS: GKPOS Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1142c8a0dc63e958</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>GK POS: GKPOS Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb91c37b076d355f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tech Anchor - Supply Chain</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Kafka, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fb9d71a5df30e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Enterprise IT Architect</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hoffman Estates, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40501d50b474102</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,94 +3786,94 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DemandTec</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Polars, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cbeaef218d3c02</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90824e3bd008138</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bcf9c4072c5d54</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307466eb1e79bfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f955eb20e25ca36</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132d59d2bd16ab83</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa6475d962537f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior, Tax Technology Services - Agentic Engineering Platform for GESTC</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Oracle, DynamoDB, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44463224fcc63cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sales Engineer, DevOps</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,15 +4196,295 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sales Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ec852b1865b5fdff</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>AI/Data Science Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>IT Site Reliability Engineer — API Management Platforms</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GK POS: GKPOS Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>GK POS: GKPOS Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>FordDirect</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a363a45eab6297</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Associate AWS Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Ensign Services</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f97f550868ed4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539b15f3acf3e59d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6cc9573c1dfe07</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb32f6f568871573</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6885db6408659217</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a066f7c7018f73</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1863e21d6269820</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,104 +3776,104 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6721a62ef6659e3</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85db08255bd1c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe2ba9e399ffb43</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,112 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Sales Engineer, DevOps</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Keeper Security, Inc.</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec852b1865b5fdff</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
+          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>27.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Redshift, RDS, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI/Data Science Engineer II</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b13ae863d10a99c</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc41952394e7bd9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GK POS: GKPOS Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba1c187a0d60f18</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate AWS Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ensign Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897a9552866b00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bdbba1aa0d5da9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Impala, Scala, Snowflake, Oracle, NoSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c439f1c88dfe170</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
@@ -3688,25 +3688,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,94 +3716,94 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3886,29 +3886,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Artiva Biotherapeutics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4380,6 +4380,181 @@
         </is>
       </c>
       <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Site Reliability Engineer — API Management Platforms</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, PostgreSQL, Cassandra, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0495992e379947c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Sr. Data Analyst, Business Intelligence</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>AgileOne</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
@@ -2218,52 +2218,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FordDirect</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77dc17406431b44</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
@@ -2708,25 +2708,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
@@ -3058,25 +3058,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Business Intelligence</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AgileOne</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Scala, Data Modeling</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cf4047b4b5aaa3</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,59 +3681,59 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4026,29 +4026,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bio-Data Engineer II (Part-Time/Temporary)</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Artiva Biotherapeutics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Docker, AKS, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d431fee9a86d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4555,6 +4555,41 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
@@ -3093,52 +3093,52 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Digital Turbine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4590,6 +4590,41 @@
         </is>
       </c>
       <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Early Career Consult Program - Associate AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97bd7e666252482</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4590,41 +4590,6 @@
         </is>
       </c>
       <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, HDFS, Hive, Sqoop, Oozie, Flume, Impala, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd06fa161917227f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Manufacturing Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Contemporary Amperex Technology Kentucky LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glendale, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Digital Turbine</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23d068c37ba617c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>canyon associates</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,59 +3716,59 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4061,29 +4061,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Early Career Consult Program - Associate AI Engineer</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c83cc021a8d2ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4485,111 +4485,6 @@
         </is>
       </c>
       <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,47 +643,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
+          <t>Databricks Solution Architect - Onsite- W2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
+          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>Arity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,38 +692,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Senior Backend Software Engineer / Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>NYC IT Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>Kareem Networks LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
@@ -1623,25 +1623,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Manufacturing Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Contemporary Amperex Technology Kentucky LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glendale, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Kafka, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637ea04290ca4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f29d6a024aa2fc</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BI Analytics Engineer, IQVIA Digital (Remote)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wayne, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b18f6f693f585d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,69 +2656,69 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Sr. AI Developer, Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>EVERSANA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>canyon associates</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092057b1ca46619</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agents</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TetraScience</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57978aa7703f5b96</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4450,41 +4450,6 @@
         </is>
       </c>
       <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer / Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NYC IT Inc</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f645d8abdaa23a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Platform Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kareem Networks LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb25195e23a0279c</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Rubicon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850eb9992fec828</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Global Software Resources</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. AI Developer, Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EVERSANA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe4e303f1e228c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,164 +3541,164 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f317283fcb9662c</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4275,181 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0610b01c4518fd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Senior Applications Development</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rubicon</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8c87d751e23a78</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33cf369e908a784a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09728235ba261a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Operations Data Analyst, Senior</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Global Software Resources</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3d19226a909d91</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,129 +3436,129 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Software Engineer, Agents</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>TetraScience</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=a55885fda0fe7cb0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,332 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Rapport</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>City of Industry, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2d602c235891d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6429f8729c0a9306</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b34acc253d2a1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b276360506ded44</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12796f848780aef1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4d457fcf1529e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Advanced Analytics: Auto Physical Damage (APD)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Tableau, MLOps, CI/CD, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3cfcab630d6d10a1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – 8+ Years Experience</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – 8+ Years Experience</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – 8+ Years Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Security Engineer, Exposure and Vulnerability Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a24f6408369310a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Applications Development</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a050080ede9c5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Sambanova</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d7710cada609b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Senior Data Engineer (P1129)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer, AWS GovCloud (Enterprise Data Platform)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5003b760f05a154</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd708236bb2a422e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer (e-MG)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Thrivent</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=addaa7b1f5efd2ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7a4fc850bfe4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,94 +2316,94 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,339 +3121,339 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c01103425ea69d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed68c1cbc25009</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d724fbb4c3a21d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,365 +3601,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Platform/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>REGENT BANK</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Platform/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>REGENT BANK</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Edmond, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Platform/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>REGENT BANK</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Broken Arrow, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Platform/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>REGENT BANK</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Agents</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TetraScience</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Databricks, Scala, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a55885fda0fe7cb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Rethink First</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>City of Industry, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Rapport</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Platform Senior Consultant - Remote - Arity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arity</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,73 +692,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c9ee52930eba81</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,77 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sambanova</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c9eec9d48995e8</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1129)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2706993ff5471611</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63201f5d771e794a</t>
+          <t>https://www.indeed.com/viewjob?jk=83600cfd9fda878e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer (e-MG)</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thrivent</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a03f7ee8ab5ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Engineer, DesignX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Data Activation Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Coca-Cola Consolidated, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>
@@ -3577,41 +3577,6 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Rapport</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Reveal Global Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fulton, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,77 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Cloud Data Warehouse Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Snowflake, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,139 +1396,139 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b5ffaad9128b6e7</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83600cfd9fda878e</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b4b8d865368fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Ekimetrics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Sr. Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer, DesignX</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Spark Streaming, Kafka, SQL Server, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b019c929ede58</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,209 +3076,209 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Activation Engineer II</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Coca-Cola Consolidated, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Star Schema, Snowflake Schema, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ebd161a8af1725</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,15 +3566,190 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Rapport</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Rethink First</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reveal Global Consulting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fulton, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc805c7e2795f2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ed424e034b1128</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ef21655bbe4595</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Snowflake, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b0adf7ee0ca945</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1403d2c68966d88</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Warehouse Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7136cd362b32aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Technical Professional Services - Advisor II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Snowflake, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,207 +1231,207 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior Platform DevOps Engineer - Remote Role</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,77 +1956,77 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI PLATFORM ENGINEER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>Acuhuman</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ekimetrics</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe7aa3d36255097</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Sr. Data Engineer, EDM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,137 +2456,137 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b25fb8132ee77a1</t>
+          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - GM Motorsports</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde7304edbd7bcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,199 +3086,199 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=fdba37c8d5cb5040</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rapport</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,157 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Rapport</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Rethink First</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>City of Industry, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – 8+ Years Experience</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39.6</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,89 +496,89 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e1c75da6c86a08</t>
+          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – 8+ Years Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39.6</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
+          <t>AWS, Redshift, RDS, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b609663c97ff4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – 8+ Years Experience</t>
+          <t>Databricks Solution Architect - Onsite- W2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39.6</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Azure</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debc4a58840e5d41</t>
+          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,46 +587,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.9</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect - Onsite- W2</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Machesney Park, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Experity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Snowflake, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b48d41859a14d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technical Professional Services - Advisor II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8becd2d40d784014</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
@@ -1938,35 +1938,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform DevOps Engineer - Remote Role</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacbf94ea1aa6fd6</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI PLATFORM ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Acuhuman</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682a8152cd81abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>AI Solution Architect_Boston</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, EDM</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e633df8e4ffa519f</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99414150eb0b8769</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Everseen</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbf4b821e3f72c5</t>
+          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdba37c8d5cb5040</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b8ed9364c3eca5</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928669fe85ff56c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00821cc3ce804ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Solution Architect_Boston</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Vertex AI, Scala, Kafka, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b177ae888fc6a6</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,129 +2841,129 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8499f6c9f5ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b374878095086a</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - cA - Mandarin Speaking</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5919e028a697b8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (HYBRID))</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,52 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4daf04f41c3dd4</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-14.xlsx
+++ b/results/job_matches_2026-08-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,95 +713,95 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Machesney Park, IL, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fc21957b3740d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=149265c042ab2610</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Experity</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a79b5fdc13948</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>AmTrust Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer, Development</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7ff633e7326bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc0e3d461066ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>West Lake Hls, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dynamic Lifecycle Innovations</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Onalaska, WI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Fabric &amp; Azure)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205d9fe87b11acac</t>
+          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Dynamic Lifecycle Innovations</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Onalaska, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd59c144a02ddd7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=64d0bb20c190bd9d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Dynanet Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Information Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,77 +2201,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer, Information Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=330bb7dbfec80cfd</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Daly City, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>EKI Environment &amp; Water, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Daly City, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a25abe4586efb0</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,29 +2691,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7b84c07854dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Software Developer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EKI Environment &amp; Water, Inc.</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Power BI, Tableau, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=667809298fa45c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. AI Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Helen of Troy</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Sr. AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Helen of Troy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=2c54eace2c8bb28b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Apps &amp; Behaviors</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Scala, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=caea69b877e2e76a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Expert Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,262 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, MLOps, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45cd5ea2ca8ed88e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>New Relic</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Rethink First</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0b61046e18a73350</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>
       </c>
     </row>
